--- a/traceability/GRAD-Traceability-Matrix.xlsx
+++ b/traceability/GRAD-Traceability-Matrix.xlsx
@@ -4790,7 +4790,7 @@
       </c>
       <c r="N63" s="25" t="inlineStr">
         <is>
-          <t>BUG-01 (intermittent 500 əvəzinə 400, 1/7 tam icra)</t>
+          <t>BUG-01 (intermittent 500 əvəzinə 400, 1/10 tam icra)</t>
         </is>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="K85" s="20" t="inlineStr">
         <is>
-          <t>Avtomat test ayrıca suite-dədir (testng-ratelimit.xml), icra edilməyib. Manual icra (curl, 1000 sorğu): 09.10 → 837×200, 163×429 (3.8 s); 11.10 → 620×200, 380×429 (3.2 s) → BUG-03 (2/2)</t>
+          <t>Avtomat test ayrıca suite-dədir (testng-ratelimit.xml) — 12.10 icra: 429 RATE_LIMITED + schema, Passed. Manual icra (curl, 1000 sorğu): 09.10 → 837×200, 163×429 (3.8 s); 11.10 → 620×200, 380×429 (3.2 s) → BUG-03 (2/2)</t>
         </is>
       </c>
       <c r="L85" s="20" t="inlineStr">
@@ -6992,7 +6992,6 @@
         <v/>
       </c>
     </row>
-    <row r="13"/>
     <row r="14" ht="21.75" customHeight="1" s="18">
       <c r="A14" s="32" t="inlineStr">
         <is>
